--- a/Zinc/5. Statistical data analysis/Identifying stream typology plots/PCA_loadings.xlsx
+++ b/Zinc/5. Statistical data analysis/Identifying stream typology plots/PCA_loadings.xlsx
@@ -395,10 +395,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0463895532046954</v>
+        <v>-0.0571524050370998</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.166107982818709</v>
+        <v>-0.140359030761124</v>
       </c>
     </row>
     <row r="3">
@@ -406,10 +406,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.218259071008179</v>
+        <v>-0.238406630599717</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0842343187030835</v>
+        <v>-0.0319363516886049</v>
       </c>
     </row>
     <row r="4">
@@ -417,10 +417,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0983884240193051</v>
+        <v>-0.141758352012814</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.558453035924191</v>
+        <v>-0.54449135796826</v>
       </c>
     </row>
     <row r="5">
@@ -428,10 +428,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.331361921142</v>
+        <v>-0.319942028878506</v>
       </c>
       <c r="C5" t="n">
-        <v>0.396212983112193</v>
+        <v>0.419303183618877</v>
       </c>
     </row>
     <row r="6">
@@ -439,10 +439,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.383115382366156</v>
+        <v>-0.377300292839088</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0335122296138071</v>
+        <v>-0.0275363335160184</v>
       </c>
     </row>
     <row r="7">
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.385520861615663</v>
+        <v>-0.378737893490555</v>
       </c>
       <c r="C7" t="n">
-        <v>0.26762449516373</v>
+        <v>0.286213463125603</v>
       </c>
     </row>
     <row r="8">
@@ -461,10 +461,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.334038768871829</v>
+        <v>-0.317493702212341</v>
       </c>
       <c r="C8" t="n">
-        <v>0.427906959162439</v>
+        <v>0.452238939049731</v>
       </c>
     </row>
     <row r="9">
@@ -472,10 +472,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.375838896142018</v>
+        <v>-0.372634199437538</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.229199809499079</v>
+        <v>-0.234134964803646</v>
       </c>
     </row>
     <row r="10">
@@ -483,10 +483,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.420336006442392</v>
+        <v>-0.418246806002459</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.156641507455489</v>
+        <v>-0.163824041539224</v>
       </c>
     </row>
     <row r="11">
@@ -494,10 +494,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.325280061318164</v>
+        <v>-0.342126815183997</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.40439927806513</v>
+        <v>-0.371671172905621</v>
       </c>
     </row>
   </sheetData>
